--- a/templates/financial-reports/non_financial_kpis_template.xlsx
+++ b/templates/financial-reports/non_financial_kpis_template.xlsx
@@ -32,8 +32,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="9">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="58" formatCode="m/d/yy"/>
+    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -398,6 +406,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C19"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="18"/>
+    <col min="2" max="2" customWidth="1" width="68.25"/>
+    <col min="3" max="3" customWidth="1" width="14.3359375"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -461,9 +474,6 @@
       <c r="B6" t="str">
         <v>Number of new products, new systems/Automations, budget for R&amp;D</v>
       </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -477,20 +487,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
       <c r="B8" t="str">
-        <v>Trainings and Certifications</v>
+        <v>Trainings and Certfications</v>
       </c>
       <c r="C8" t="str">
         <v>number of Trainings Done</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v/>
-      </c>
       <c r="B9" t="str">
         <v>Employee Engagement</v>
       </c>
@@ -499,11 +503,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
       <c r="B10" t="str">
-        <v>Health and Safety</v>
+        <v>Healthy and Safety</v>
       </c>
       <c r="C10" t="str">
         <v>trainings done on safety</v>
@@ -513,44 +514,23 @@
       <c r="A11" t="str">
         <v>ESG</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Governance</v>
+        <v>Gorvanance</v>
       </c>
       <c r="B12" t="str">
         <v>Frequency of Board Meetings</v>
       </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v/>
-      </c>
       <c r="B13" t="str">
         <v>Board Composition</v>
       </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v/>
-      </c>
       <c r="B14" t="str">
         <v>Timely management reports</v>
-      </c>
-      <c r="C14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -560,55 +540,32 @@
       <c r="B15" t="str">
         <v>Emissions &amp; Waste reduced</v>
       </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v/>
-      </c>
       <c r="B16" t="str">
         <v>Accident reduced</v>
       </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
+    </row>
+    <row r="17" ht="17" customHeight="1">
       <c r="A17" t="str">
         <v>Social</v>
       </c>
       <c r="B17" t="str">
         <v>Empowerment; Youth, Women, disadvantaged</v>
       </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v/>
-      </c>
       <c r="B18" t="str">
         <v>Jobs created</v>
       </c>
-      <c r="C18" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v/>
-      </c>
       <c r="B19" t="str">
         <v>CSR activities</v>
       </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
   </ignoredErrors>
